--- a/outputs/cream/silpo_novus/primary_chain_output.xlsx
+++ b/outputs/cream/silpo_novus/primary_chain_output.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="PreTests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ModelCoefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ResidualDiagnostics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SeriesUsed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LagProfile" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ModelEligibility" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="NARDL_Multipliers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VECM_IRF" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,19 +518,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.166352131060911e-05</v>
+        <v>3.166352131058586e-05</v>
       </c>
       <c r="C2" t="n">
         <v>0.01</v>
       </c>
       <c r="D2" t="n">
-        <v>1.807358615624225e-13</v>
+        <v>1.807358615622328e-13</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.250471045105603e-20</v>
+        <v>2.250471045106072e-20</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
@@ -574,13 +574,13 @@
         <v>0.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.604635633535988e-13</v>
+        <v>3.604635633536289e-13</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169300175083072e-11</v>
+        <v>1.169300175082499e-11</v>
       </c>
       <c r="G3" t="n">
         <v>0.09309066682789993</v>
@@ -624,13 +624,13 @@
         <v>0.02241119506040381</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06219840162312722</v>
+        <v>0.06219840162312693</v>
       </c>
       <c r="E4" t="n">
         <v>0.1</v>
       </c>
       <c r="F4" t="n">
-        <v>9.358690774180871e-07</v>
+        <v>9.358690774186149e-07</v>
       </c>
       <c r="G4" t="n">
         <v>0.1</v>
